--- a/dados_excel/teams_infos.xlsx
+++ b/dados_excel/teams_infos.xlsx
@@ -33,12 +33,18 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor auto="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -69,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -83,6 +89,10 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -276,8 +286,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:K98" headerRowCount="1" headerRowDxfId="13" dataDxfId="12" totalsRowDxfId="11">
-  <autoFilter ref="A1:K98"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:K106" headerRowCount="1" headerRowDxfId="13" dataDxfId="12" totalsRowDxfId="11">
+  <autoFilter ref="A1:K106"/>
   <sortState ref="A2:I98">
     <sortCondition ref="C1:C98"/>
   </sortState>
@@ -451,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z106"/>
+  <dimension ref="A1:Z110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="6.5" customWidth="1" min="1" max="1"/>
@@ -5798,237 +5808,439 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="8" t="n"/>
+      <c r="A99" s="9" t="n">
+        <v>2840</v>
+      </c>
+      <c r="B99" s="11" t="inlineStr">
+        <is>
+          <t>sixa_eaters</t>
+        </is>
+      </c>
+      <c r="C99" s="11" t="inlineStr">
+        <is>
+          <t>sixA Eaters</t>
+        </is>
+      </c>
+      <c r="D99" s="11" t="inlineStr">
+        <is>
+          <t>SIXA</t>
+        </is>
+      </c>
+      <c r="E99" s="11" t="inlineStr">
+        <is>
+          <t>Universidade Federal do ABC</t>
+        </is>
+      </c>
+      <c r="F99" s="11" t="inlineStr">
+        <is>
+          <t>UFABC</t>
+        </is>
+      </c>
+      <c r="G99" s="11" t="inlineStr">
+        <is>
+          <t>assets\team-logos\axis_anteaters.png</t>
+        </is>
+      </c>
+      <c r="H99" s="11" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/axis_anteaters/</t>
+        </is>
+      </c>
+      <c r="I99" s="11" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="J99" s="12" t="inlineStr">
+        <is>
+          <t>2b772b</t>
+        </is>
+      </c>
+      <c r="K99" s="12" t="inlineStr">
+        <is>
+          <t>e1e3e2</t>
+        </is>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" s="3" t="n"/>
+      <c r="A100" s="10" t="n">
+        <v>2841</v>
+      </c>
+      <c r="B100" s="11" t="inlineStr">
+        <is>
+          <t>minerva_artemis</t>
+        </is>
+      </c>
+      <c r="C100" s="11" t="inlineStr">
+        <is>
+          <t>Minerva Artemis</t>
+        </is>
+      </c>
+      <c r="D100" s="11" t="inlineStr">
+        <is>
+          <t>ARTMS</t>
+        </is>
+      </c>
+      <c r="E100" s="11" t="inlineStr">
+        <is>
+          <t>Universidade Federal do Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="F100" s="11" t="inlineStr">
+        <is>
+          <t>UFRJ</t>
+        </is>
+      </c>
+      <c r="G100" s="11" t="inlineStr">
+        <is>
+          <t>assets\team-logos\ufrj_minerva.png</t>
+        </is>
+      </c>
+      <c r="H100" s="11" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/minervaesports/</t>
+        </is>
+      </c>
+      <c r="I100" s="11" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="J100" s="12" t="inlineStr">
+        <is>
+          <t>131732</t>
+        </is>
+      </c>
+      <c r="K100" s="12" t="inlineStr">
+        <is>
+          <t>fdc725</t>
+        </is>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" s="8" t="n"/>
+      <c r="A101" s="9" t="n">
+        <v>2842</v>
+      </c>
+      <c r="B101" s="11" t="inlineStr">
+        <is>
+          <t>a2e_uff_shadows</t>
+        </is>
+      </c>
+      <c r="C101" s="11" t="inlineStr">
+        <is>
+          <t>A2E UFF Shadows</t>
+        </is>
+      </c>
+      <c r="D101" s="11" t="inlineStr">
+        <is>
+          <t>A2E S</t>
+        </is>
+      </c>
+      <c r="E101" s="11" t="inlineStr">
+        <is>
+          <t>Universidade Federal Fluminense</t>
+        </is>
+      </c>
+      <c r="F101" s="11" t="inlineStr">
+        <is>
+          <t>UFF</t>
+        </is>
+      </c>
+      <c r="G101" s="11" t="inlineStr">
+        <is>
+          <t>assets\team-logos\a2e_uff.png</t>
+        </is>
+      </c>
+      <c r="H101" s="11" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/a2euff/</t>
+        </is>
+      </c>
+      <c r="I101" s="11" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="J101" s="12" t="inlineStr">
+        <is>
+          <t>7617ad</t>
+        </is>
+      </c>
+      <c r="K101" s="12" t="inlineStr">
+        <is>
+          <t>a388f8</t>
+        </is>
+      </c>
     </row>
     <row r="102">
-      <c r="A102" s="8" t="n"/>
+      <c r="A102" s="9" t="n">
+        <v>2843</v>
+      </c>
+      <c r="B102" s="11" t="inlineStr">
+        <is>
+          <t>sheriff_iff</t>
+        </is>
+      </c>
+      <c r="C102" s="11" t="inlineStr">
+        <is>
+          <t>Sheriff IFF</t>
+        </is>
+      </c>
+      <c r="D102" s="11" t="inlineStr">
+        <is>
+          <t>SHF</t>
+        </is>
+      </c>
+      <c r="E102" s="11" t="inlineStr">
+        <is>
+          <t>Instituto Federal de Educação, Ciência e Tecnologia Fluminense</t>
+        </is>
+      </c>
+      <c r="F102" s="11" t="inlineStr">
+        <is>
+          <t>IFF</t>
+        </is>
+      </c>
+      <c r="G102" s="11" t="inlineStr">
+        <is>
+          <t>assets\team-logos\sheriff.png</t>
+        </is>
+      </c>
+      <c r="H102" s="11" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/atleticasheriff.esports/</t>
+        </is>
+      </c>
+      <c r="I102" s="11" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="J102" s="12" t="inlineStr">
+        <is>
+          <t>f9b70b</t>
+        </is>
+      </c>
+      <c r="K102" s="12" t="inlineStr">
+        <is>
+          <t>775e25</t>
+        </is>
+      </c>
     </row>
     <row r="103">
-      <c r="A103" t="n">
-        <v>2840</v>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>sixa_eaters</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>sixA Eaters</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>SIXA</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>Universidade Federal do ABC</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>UFABC</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>assets\team-logos\axis_anteaters.png</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/axis_anteaters/</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>2b772b</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>e1e3e2</t>
+      <c r="A103" s="11" t="n">
+        <v>2844</v>
+      </c>
+      <c r="B103" s="11" t="inlineStr">
+        <is>
+          <t>ufu_saints_trigons</t>
+        </is>
+      </c>
+      <c r="C103" s="11" t="inlineStr">
+        <is>
+          <t>UFU Saints Trigons</t>
+        </is>
+      </c>
+      <c r="D103" s="11" t="inlineStr">
+        <is>
+          <t>UFU T</t>
+        </is>
+      </c>
+      <c r="E103" s="11" t="inlineStr">
+        <is>
+          <t>Universidade Federal de Uberlândia</t>
+        </is>
+      </c>
+      <c r="F103" s="11" t="inlineStr">
+        <is>
+          <t>UFU</t>
+        </is>
+      </c>
+      <c r="G103" s="11" t="inlineStr">
+        <is>
+          <t>assets\team-logos\ufu_saints.png</t>
+        </is>
+      </c>
+      <c r="H103" s="11" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ufuesports/</t>
+        </is>
+      </c>
+      <c r="I103" s="11" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="J103" s="12" t="inlineStr">
+        <is>
+          <t>fefefe</t>
+        </is>
+      </c>
+      <c r="K103" s="12" t="inlineStr">
+        <is>
+          <t>d7ad00</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="n">
-        <v>2841</v>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>minerva_artemis</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Minerva Artemis</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>ARTMS</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>Universidade Federal do Rio de Janeiro</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>UFRJ</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>assets\team-logos\ufrj_minerva.png</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/minervaesports/</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>RJ</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>131732</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>fdc725</t>
+      <c r="A104" s="11" t="n">
+        <v>2845</v>
+      </c>
+      <c r="B104" s="11" t="inlineStr">
+        <is>
+          <t>green_owls_jacurutu</t>
+        </is>
+      </c>
+      <c r="C104" s="11" t="inlineStr">
+        <is>
+          <t>Green Owls Jacurutu</t>
+        </is>
+      </c>
+      <c r="D104" s="11" t="inlineStr">
+        <is>
+          <t>OWL J</t>
+        </is>
+      </c>
+      <c r="E104" s="11" t="inlineStr">
+        <is>
+          <t>Universidade de Brasília</t>
+        </is>
+      </c>
+      <c r="F104" s="11" t="inlineStr">
+        <is>
+          <t>UnB</t>
+        </is>
+      </c>
+      <c r="G104" s="11" t="inlineStr">
+        <is>
+          <t>assets\team-logos\green_owls.png</t>
+        </is>
+      </c>
+      <c r="H104" s="11" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/unbgreenowls/</t>
+        </is>
+      </c>
+      <c r="I104" s="11" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="J104" s="12" t="inlineStr">
+        <is>
+          <t>00a675</t>
+        </is>
+      </c>
+      <c r="K104" s="12" t="inlineStr">
+        <is>
+          <t>043a58</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="n">
-        <v>2842</v>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>a2e_uff_shadows</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>A2E UFF Shadows</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>A2E S</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Universidade Federal Fluminense</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>UFF</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>assets\team-logos\a2e_uff.png</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/a2euff/</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>RJ</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>7617ad</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>a388f8</t>
+      <c r="A105" s="11" t="n">
+        <v>2846</v>
+      </c>
+      <c r="B105" s="11" t="inlineStr">
+        <is>
+          <t>nox_unievangelica</t>
+        </is>
+      </c>
+      <c r="C105" s="11" t="inlineStr">
+        <is>
+          <t>NOX UniEvangélica</t>
+        </is>
+      </c>
+      <c r="D105" s="11" t="inlineStr">
+        <is>
+          <t>NOX</t>
+        </is>
+      </c>
+      <c r="E105" s="11" t="inlineStr">
+        <is>
+          <t>Universidade Evangélica de Goiás</t>
+        </is>
+      </c>
+      <c r="F105" s="11" t="inlineStr">
+        <is>
+          <t>UniEvangélica</t>
+        </is>
+      </c>
+      <c r="G105" s="11" t="inlineStr">
+        <is>
+          <t>assets\team-logos\uniEvangelica_nox.png</t>
+        </is>
+      </c>
+      <c r="H105" s="11" t="n"/>
+      <c r="I105" s="11" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="J105" s="12" t="n">
+        <v>20202</v>
+      </c>
+      <c r="K105" s="12" t="inlineStr">
+        <is>
+          <t>e44239</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="n">
-        <v>2843</v>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>sheriff_iff</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Sheriff IFF</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>SHF</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>Instituto Federal de Educação, Ciência e Tecnologia Fluminense</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>IFF</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>assets\team-logos\sheriff.png</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/atleticasheriff.esports/</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>RJ</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>f9b70b</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>775e25</t>
-        </is>
-      </c>
-    </row>
+      <c r="A106" s="11" t="n">
+        <v>2847</v>
+      </c>
+      <c r="B106" s="11" t="inlineStr">
+        <is>
+          <t>sistematica_unievangelica</t>
+        </is>
+      </c>
+      <c r="C106" s="11" t="inlineStr">
+        <is>
+          <t>Sistemática UniEvangélica</t>
+        </is>
+      </c>
+      <c r="D106" s="11" t="inlineStr">
+        <is>
+          <t>SIST U</t>
+        </is>
+      </c>
+      <c r="E106" s="11" t="inlineStr">
+        <is>
+          <t>Universidade Evangélica de Goiás</t>
+        </is>
+      </c>
+      <c r="F106" s="11" t="inlineStr">
+        <is>
+          <t>UniEvangélica</t>
+        </is>
+      </c>
+      <c r="G106" s="11" t="inlineStr">
+        <is>
+          <t>assets\team-logos\uniEvangelica_Sistematica.png</t>
+        </is>
+      </c>
+      <c r="H106" s="11" t="n"/>
+      <c r="I106" s="11" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="J106" s="12" t="inlineStr">
+        <is>
+          <t>4c4ea6</t>
+        </is>
+      </c>
+      <c r="K106" s="12" t="inlineStr">
+        <is>
+          <t>dcc7c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>

--- a/dados_excel/teams_infos.xlsx
+++ b/dados_excel/teams_infos.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="teams" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="teams" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z110"/>
+  <dimension ref="A1:Z115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="6.5" customWidth="1" min="1" max="1"/>
@@ -6237,10 +6237,471 @@
         </is>
       </c>
     </row>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>2848</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>ufrn_tirana</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>UFRN Tirana</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>TIR</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Universidade Federal do Rio Grande do Norte</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>UFRN</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>assets\team-logos\tirana.png</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>RN</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>f07436</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>282828</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>2849</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>ufu_saints_onyx</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>UFU Saints Onyx</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>UFU O</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Universidade Federal de Uberlândia</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>UFU</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>assets\team-logos\ufu_saints.png</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ufuesports/</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>fefefe</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>d7ad00</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>2850</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>incinera_esports</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Incinera E-Sports</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>INC</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Universidade Federal de Pernambuco</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>UFPE</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>assets\team-logos\incinera.png</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>e66b12</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>020101</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>2851</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>azure_bears_spotline</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Azure Bears Spotline</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>AZR SP</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Universidade Tecnológica Federal do Paraná</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>UTFPR Curitiba</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>assets\team-logos\azure_bears.png</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/azure_bears/</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>037aff</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>fefeff</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>2852</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>azure_bears_polaris</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Azure Bears Polaris</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>AZR P</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Universidade Tecnológica Federal do Paraná</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>UTFPR Curitiba</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>assets\team-logos\azure_bears.png</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/azure_bears/</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>037aff</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>fefeff</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>2853</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>fei_last_dance</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>FEI Last Dance</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>FEI LD</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Fundação Educacional Inaciana</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>FEI</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>assets\team-logos\fei_darkowls.png</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/darkowls_fei/</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>242323</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>fac60a</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>2854</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>fei_capim</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>FEI Capim</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>FEI C</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Fundação Educacional Inaciana</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>FEI</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>assets\team-logos\fei_whiteowls.png</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/darkowls_fei/</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>242323</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>fdfdfd</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>2855</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>macklogic_wine</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>MackLogic Wine</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>LOGIC W</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Instituto Presbiteriano Mackenzie</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Mackenzie</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>assets\team-logos\macklogic_wine.png</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mackenzielogic/</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>78061d</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>78061d</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>2856</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>atletica_sustenta</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Atlética Sustenta</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>assets\team-logos\atletica_sustenta.png</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>6d0407</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>c38d4d</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>

--- a/dados_excel/teams_infos.xlsx
+++ b/dados_excel/teams_infos.xlsx
@@ -533,7 +533,11 @@
           <t>cor2</t>
         </is>
       </c>
-      <c r="L1" s="2" t="n"/>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>sucede</t>
+        </is>
+      </c>
       <c r="M1" s="2" t="n"/>
       <c r="N1" s="2" t="n"/>
       <c r="O1" s="2" t="n"/>
@@ -980,6 +984,11 @@
           <t>fefeff</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>azure_bears</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -1530,6 +1539,11 @@
           <t>fdfdfd</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>axis_ego</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
@@ -3266,6 +3280,11 @@
           <t>fdc725</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>dark_ufrj</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
@@ -6286,6 +6305,11 @@
           <t>282828</t>
         </is>
       </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>ufrn_carcaras</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -6341,6 +6365,11 @@
           <t>d7ad00</t>
         </is>
       </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>ufu_saints_trigons</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -6389,6 +6418,11 @@
       <c r="K109" t="inlineStr">
         <is>
           <t>020101</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>ufpe_virtus</t>
         </is>
       </c>
     </row>
